--- a/files/growth_options_model.xlsx
+++ b/files/growth_options_model.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Autumn Harvest Festival: Growth Option Evaluation (Part 3)</t>
   </si>
   <si>
-    <t xml:space="preserve">WDPR Fall 2026 IE Case Study, Part 3. Built September 2026. Uses outputs of Parts 1 and 2.</t>
+    <t xml:space="preserve">WDPR 2026 IE Case Study, Part 3. Built in 2026. Uses outputs of Parts 1 and 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Question</t>
